--- a/Project/DiceWarrior/LubanTool/Datas/敌人表.xlsx
+++ b/Project/DiceWarrior/LubanTool/Datas/敌人表.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="27">
   <si>
     <t>##var</t>
   </si>
@@ -120,10 +120,18 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -273,7 +281,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -282,6 +290,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor theme="4" tint="0.599993896298105"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor theme="4" tint="0.799981688894314"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -467,11 +493,163 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="21">
     <border>
       <left/>
       <right/>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thick">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thick">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -593,141 +771,198 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1255,222 +1490,304 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="6"/>
+  <dimension ref="A1:H33"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="8.54545454545454" customWidth="1"/>
-    <col min="2" max="2" width="5.54545454545455" customWidth="1"/>
-    <col min="3" max="4" width="10.6363636363636" customWidth="1"/>
-    <col min="5" max="5" width="10.2727272727273" customWidth="1"/>
-    <col min="6" max="6" width="7.54545454545455" customWidth="1"/>
-    <col min="7" max="7" width="18.5454545454545" customWidth="1"/>
+    <col min="1" max="1" width="8.54545454545454" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5454545454545" style="1" customWidth="1"/>
+    <col min="3" max="4" width="10.6363636363636" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7272727272727" style="1" customWidth="1"/>
+    <col min="6" max="6" width="23.6363636363636" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5454545454545" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.72727272727273" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="25" customHeight="1" spans="1:8">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="4"/>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="1" t="s">
+    <row r="2" ht="25" customHeight="1" spans="1:8">
+      <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="7"/>
     </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="1" t="s">
+    <row r="3" ht="25" customHeight="1" spans="1:8">
+      <c r="A3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="9" t="s">
         <v>10</v>
       </c>
+      <c r="H3" s="10"/>
     </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="1" t="s">
+    <row r="4" ht="25" customHeight="1" spans="1:8">
+      <c r="A4" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="13"/>
     </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="1" t="s">
+    <row r="5" ht="25" customHeight="1" spans="1:8">
+      <c r="A5" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="9" t="s">
         <v>17</v>
       </c>
+      <c r="H5" s="10"/>
     </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1">
+    <row r="6" ht="25" customHeight="1" spans="1:8">
+      <c r="A6" s="11"/>
+      <c r="B6" s="12">
         <v>1</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="12">
         <v>10</v>
       </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1">
+      <c r="F6" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="12">
         <v>1</v>
       </c>
+      <c r="H6" s="13"/>
     </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1">
+    <row r="7" ht="25" customHeight="1" spans="1:8">
+      <c r="A7" s="8"/>
+      <c r="B7" s="9">
         <v>2</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="9">
         <v>10</v>
       </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1">
+      <c r="F7" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="9">
         <v>2</v>
       </c>
+      <c r="H7" s="10"/>
     </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1">
+    <row r="8" ht="25" customHeight="1" spans="1:8">
+      <c r="A8" s="11"/>
+      <c r="B8" s="12">
         <v>3</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="12">
         <v>10</v>
       </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1">
+      <c r="F8" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" s="12">
         <v>3</v>
       </c>
+      <c r="H8" s="13"/>
     </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1">
+    <row r="9" ht="25" customHeight="1" spans="1:8">
+      <c r="A9" s="8"/>
+      <c r="B9" s="9">
         <v>4</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" s="9">
         <v>10</v>
       </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1">
+      <c r="F9" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" s="9">
         <v>4</v>
       </c>
+      <c r="H9" s="10"/>
     </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1">
+    <row r="10" ht="25" customHeight="1" spans="1:8">
+      <c r="A10" s="11"/>
+      <c r="B10" s="12">
         <v>1001</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10" s="12">
         <v>50</v>
       </c>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1" t="s">
+      <c r="F10" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" s="12" t="s">
         <v>25</v>
       </c>
+      <c r="H10" s="13"/>
     </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1">
+    <row r="11" ht="25" customHeight="1" spans="1:8">
+      <c r="A11" s="8"/>
+      <c r="B11" s="9">
         <v>9001</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11" s="9">
         <v>200</v>
       </c>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1">
+      <c r="F11" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="9">
         <v>9001</v>
       </c>
+      <c r="H11" s="10"/>
     </row>
+    <row r="12" ht="25" customHeight="1" spans="1:8">
+      <c r="A12" s="14"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="13"/>
+    </row>
+    <row r="13" ht="25" customHeight="1" spans="1:8">
+      <c r="A13" s="16"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="10"/>
+    </row>
+    <row r="14" ht="25" customHeight="1" spans="1:8">
+      <c r="A14" s="14"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="13"/>
+    </row>
+    <row r="15" ht="25" customHeight="1" spans="1:8">
+      <c r="A15" s="18"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="20"/>
+    </row>
+    <row r="16" ht="25" customHeight="1"/>
+    <row r="17" ht="25" customHeight="1"/>
+    <row r="18" ht="25" customHeight="1"/>
+    <row r="19" ht="25" customHeight="1"/>
+    <row r="20" ht="25" customHeight="1"/>
+    <row r="21" ht="25" customHeight="1"/>
+    <row r="22" ht="25" customHeight="1"/>
+    <row r="23" ht="25" customHeight="1"/>
+    <row r="24" ht="25" customHeight="1"/>
+    <row r="25" ht="25" customHeight="1"/>
+    <row r="26" ht="25" customHeight="1"/>
+    <row r="27" ht="25" customHeight="1"/>
+    <row r="28" ht="25" customHeight="1"/>
+    <row r="29" ht="25" customHeight="1"/>
+    <row r="30" ht="25" customHeight="1"/>
+    <row r="31" ht="25" customHeight="1"/>
+    <row r="32" ht="25" customHeight="1"/>
+    <row r="33" ht="25" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
